--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/36.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/36.xlsx
@@ -426,13 +426,13 @@
         <v>-8.759872723688302</v>
       </c>
       <c r="E2">
-        <v>-10.99753253008129</v>
+        <v>-17.0461065787504</v>
       </c>
       <c r="F2">
-        <v>-2.66689172402739</v>
+        <v>-4.403911898305729</v>
       </c>
       <c r="G2">
-        <v>-5.90462927651199</v>
+        <v>-10.94035609722895</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.232242663725899</v>
       </c>
       <c r="E3">
-        <v>-12.40609625627112</v>
+        <v>-17.37315750005836</v>
       </c>
       <c r="F3">
-        <v>-2.589971183738234</v>
+        <v>-4.594132390112788</v>
       </c>
       <c r="G3">
-        <v>-6.464221926145929</v>
+        <v>-10.07124909911415</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.678101078104836</v>
       </c>
       <c r="E4">
-        <v>-12.11365193332978</v>
+        <v>-19.40366184646164</v>
       </c>
       <c r="F4">
-        <v>-2.430407741141382</v>
+        <v>-3.712466171882357</v>
       </c>
       <c r="G4">
-        <v>-6.70590030010683</v>
+        <v>-11.09668005476401</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.02261536565704</v>
       </c>
       <c r="E5">
-        <v>-12.25178397598575</v>
+        <v>-18.45761381304522</v>
       </c>
       <c r="F5">
-        <v>-2.220002420830307</v>
+        <v>-3.927877316408549</v>
       </c>
       <c r="G5">
-        <v>-5.989255261751628</v>
+        <v>-10.68018475855902</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.27576053026032</v>
       </c>
       <c r="E6">
-        <v>-13.67888727476298</v>
+        <v>-18.45914896573382</v>
       </c>
       <c r="F6">
-        <v>-2.256286569807731</v>
+        <v>-4.170340455207964</v>
       </c>
       <c r="G6">
-        <v>-6.262157740072205</v>
+        <v>-11.1803151110927</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.43041736081993</v>
       </c>
       <c r="E7">
-        <v>-14.29575600408784</v>
+        <v>-20.82869110414336</v>
       </c>
       <c r="F7">
-        <v>-2.256017350401821</v>
+        <v>-3.376042146950796</v>
       </c>
       <c r="G7">
-        <v>-5.614572571878636</v>
+        <v>-10.75621722453447</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.49496970303521</v>
       </c>
       <c r="E8">
-        <v>-14.57753124226711</v>
+        <v>-21.56419226704716</v>
       </c>
       <c r="F8">
-        <v>-1.874654393868388</v>
+        <v>-3.695111046426304</v>
       </c>
       <c r="G8">
-        <v>-6.244038834620951</v>
+        <v>-11.23937709916271</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.4645077932958</v>
       </c>
       <c r="E9">
-        <v>-15.05779855315059</v>
+        <v>-22.5601395555541</v>
       </c>
       <c r="F9">
-        <v>-2.133984749723607</v>
+        <v>-3.797098812691577</v>
       </c>
       <c r="G9">
-        <v>-5.776261326663394</v>
+        <v>-9.958598200535294</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.3448654397321</v>
       </c>
       <c r="E10">
-        <v>-16.28440819371223</v>
+        <v>-22.17652799389034</v>
       </c>
       <c r="F10">
-        <v>-2.119843689790416</v>
+        <v>-4.006896111328996</v>
       </c>
       <c r="G10">
-        <v>-5.34420647782351</v>
+        <v>-9.564034589233625</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.13219891887688</v>
       </c>
       <c r="E11">
-        <v>-16.31338137041331</v>
+        <v>-23.73254789071794</v>
       </c>
       <c r="F11">
-        <v>-1.851332538009971</v>
+        <v>-3.02746680058757</v>
       </c>
       <c r="G11">
-        <v>-5.218847408144925</v>
+        <v>-10.08566350542479</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.836061720946118</v>
       </c>
       <c r="E12">
-        <v>-16.99835834881353</v>
+        <v>-24.23845994990685</v>
       </c>
       <c r="F12">
-        <v>-1.69733241089032</v>
+        <v>-3.46782194171137</v>
       </c>
       <c r="G12">
-        <v>-3.470356625991144</v>
+        <v>-8.933656146897784</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.463003426856414</v>
       </c>
       <c r="E13">
-        <v>-17.16245213295547</v>
+        <v>-22.69353934287206</v>
       </c>
       <c r="F13">
-        <v>-1.753041775463392</v>
+        <v>-3.104418818838033</v>
       </c>
       <c r="G13">
-        <v>-3.546202062337709</v>
+        <v>-7.313290504197201</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.032936200963059</v>
       </c>
       <c r="E14">
-        <v>-19.61674919089257</v>
+        <v>-24.17615720450932</v>
       </c>
       <c r="F14">
-        <v>-1.685491727234704</v>
+        <v>-2.909248831799247</v>
       </c>
       <c r="G14">
-        <v>-2.784256479132813</v>
+        <v>-8.113429506354032</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.566966329280723</v>
       </c>
       <c r="E15">
-        <v>-19.17410897053882</v>
+        <v>-25.64341901078658</v>
       </c>
       <c r="F15">
-        <v>-1.312800949041178</v>
+        <v>-2.981253839920191</v>
       </c>
       <c r="G15">
-        <v>-2.913349578946047</v>
+        <v>-7.342355564770762</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.083628823273228</v>
       </c>
       <c r="E16">
-        <v>-20.55387160203987</v>
+        <v>-25.91099748295181</v>
       </c>
       <c r="F16">
-        <v>-0.7237381201342135</v>
+        <v>-3.335351083390479</v>
       </c>
       <c r="G16">
-        <v>-2.826403770063881</v>
+        <v>-6.316701486054854</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.60128057489773</v>
       </c>
       <c r="E17">
-        <v>-20.91057949962407</v>
+        <v>-26.06837101166637</v>
       </c>
       <c r="F17">
-        <v>-1.145777229614714</v>
+        <v>-2.562365011672537</v>
       </c>
       <c r="G17">
-        <v>-1.787913552607425</v>
+        <v>-6.788951298997935</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.124476230450743</v>
       </c>
       <c r="E18">
-        <v>-21.3713924861706</v>
+        <v>-27.22663692250424</v>
       </c>
       <c r="F18">
-        <v>-0.5803568347510498</v>
+        <v>-2.011846946385236</v>
       </c>
       <c r="G18">
-        <v>-1.832990974391077</v>
+        <v>-6.103126774750598</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.662497825843066</v>
       </c>
       <c r="E19">
-        <v>-22.82137363563458</v>
+        <v>-28.09413404578362</v>
       </c>
       <c r="F19">
-        <v>-0.5231547521181327</v>
+        <v>-2.538523769452565</v>
       </c>
       <c r="G19">
-        <v>-0.1203245692233132</v>
+        <v>-5.073971632630763</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.213356357471524</v>
       </c>
       <c r="E20">
-        <v>-23.66738314974756</v>
+        <v>-29.09089645961194</v>
       </c>
       <c r="F20">
-        <v>0.2084344870123067</v>
+        <v>-2.344415749424168</v>
       </c>
       <c r="G20">
-        <v>-1.242784527607518</v>
+        <v>-6.340670809546598</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.783446259060997</v>
       </c>
       <c r="E21">
-        <v>-23.20127184861206</v>
+        <v>-28.7852878627303</v>
       </c>
       <c r="F21">
-        <v>0.1206391394591982</v>
+        <v>-1.824237468631801</v>
       </c>
       <c r="G21">
-        <v>-1.026739056469</v>
+        <v>-5.442085316941746</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.377971112750889</v>
       </c>
       <c r="E22">
-        <v>-24.01483937493408</v>
+        <v>-26.72834628507024</v>
       </c>
       <c r="F22">
-        <v>0.4235101427403647</v>
+        <v>-2.057115568213423</v>
       </c>
       <c r="G22">
-        <v>-1.477427962544969</v>
+        <v>-5.38120225090625</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.003746707467008</v>
       </c>
       <c r="E23">
-        <v>-24.84288443265863</v>
+        <v>-29.54788288562199</v>
       </c>
       <c r="F23">
-        <v>0.4575154529926872</v>
+        <v>-1.5438740360521</v>
       </c>
       <c r="G23">
-        <v>-1.147780038575356</v>
+        <v>-5.721907891531192</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.674968635796122</v>
       </c>
       <c r="E24">
-        <v>-24.92158478243793</v>
+        <v>-29.94938418385305</v>
       </c>
       <c r="F24">
-        <v>0.719283694114345</v>
+        <v>-1.111839017122018</v>
       </c>
       <c r="G24">
-        <v>-1.406714356717376</v>
+        <v>-5.298390781188984</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.399493180809408</v>
       </c>
       <c r="E25">
-        <v>-25.40739041703279</v>
+        <v>-29.30313697940343</v>
       </c>
       <c r="F25">
-        <v>0.9366456438741296</v>
+        <v>-2.018169874770805</v>
       </c>
       <c r="G25">
-        <v>-1.888017059942965</v>
+        <v>-4.484132682661862</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.189202425462213</v>
       </c>
       <c r="E26">
-        <v>-24.64338703872472</v>
+        <v>-30.83281247869141</v>
       </c>
       <c r="F26">
-        <v>1.152316067397398</v>
+        <v>-1.369345307956273</v>
       </c>
       <c r="G26">
-        <v>-1.216452724592974</v>
+        <v>-4.512256032647862</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.046633056373794</v>
       </c>
       <c r="E27">
-        <v>-25.56133136244954</v>
+        <v>-29.15427698182329</v>
       </c>
       <c r="F27">
-        <v>1.188568738413515</v>
+        <v>-0.7147238260569492</v>
       </c>
       <c r="G27">
-        <v>-1.701148210911029</v>
+        <v>-5.741900374492888</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.973682848852953</v>
       </c>
       <c r="E28">
-        <v>-24.5577083104996</v>
+        <v>-29.10355807293739</v>
       </c>
       <c r="F28">
-        <v>1.069573761001366</v>
+        <v>-0.430919355286019</v>
       </c>
       <c r="G28">
-        <v>-2.238028244910492</v>
+        <v>-6.514539458760014</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.968074723780997</v>
       </c>
       <c r="E29">
-        <v>-24.36897509928192</v>
+        <v>-29.07111608514644</v>
       </c>
       <c r="F29">
-        <v>1.060294389355206</v>
+        <v>-1.550428907310453</v>
       </c>
       <c r="G29">
-        <v>-2.318139269284335</v>
+        <v>-7.010614221446223</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.019691751879369</v>
       </c>
       <c r="E30">
-        <v>-23.85255698039521</v>
+        <v>-30.54834506271457</v>
       </c>
       <c r="F30">
-        <v>1.302994441231822</v>
+        <v>-1.6632981077789</v>
       </c>
       <c r="G30">
-        <v>-2.40124604894195</v>
+        <v>-6.960801996952292</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.118093787727314</v>
       </c>
       <c r="E31">
-        <v>-24.26038229257799</v>
+        <v>-29.47493369783242</v>
       </c>
       <c r="F31">
-        <v>1.352587140902623</v>
+        <v>-0.954209812410703</v>
       </c>
       <c r="G31">
-        <v>-2.166011994123799</v>
+        <v>-5.79241478040054</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.245102630436398</v>
       </c>
       <c r="E32">
-        <v>-23.97510654399078</v>
+        <v>-28.53393944140856</v>
       </c>
       <c r="F32">
-        <v>0.7416877188904604</v>
+        <v>-0.8050846274565276</v>
       </c>
       <c r="G32">
-        <v>-2.262401158654047</v>
+        <v>-6.48158943186007</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.384097855176112</v>
       </c>
       <c r="E33">
-        <v>-24.11013205347749</v>
+        <v>-28.93196513583874</v>
       </c>
       <c r="F33">
-        <v>0.8496670665801815</v>
+        <v>-1.021543656747261</v>
       </c>
       <c r="G33">
-        <v>-2.614062798065976</v>
+        <v>-6.661338030108011</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.517228850464764</v>
       </c>
       <c r="E34">
-        <v>-22.42266867010325</v>
+        <v>-27.02617949208071</v>
       </c>
       <c r="F34">
-        <v>0.9742883153921448</v>
+        <v>-0.5354526945800941</v>
       </c>
       <c r="G34">
-        <v>-2.490373870161148</v>
+        <v>-6.300052567862232</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.628411714985964</v>
       </c>
       <c r="E35">
-        <v>-22.75278989678841</v>
+        <v>-27.14911397596694</v>
       </c>
       <c r="F35">
-        <v>1.03065540368304</v>
+        <v>-1.683183895650504</v>
       </c>
       <c r="G35">
-        <v>-2.52279890161158</v>
+        <v>-6.72900338110688</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.708101852314922</v>
       </c>
       <c r="E36">
-        <v>-21.94422180577086</v>
+        <v>-27.00606853901265</v>
       </c>
       <c r="F36">
-        <v>0.9584598710594519</v>
+        <v>-1.563342326752694</v>
       </c>
       <c r="G36">
-        <v>-1.907730639072109</v>
+        <v>-5.615481470250603</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.748967281571747</v>
       </c>
       <c r="E37">
-        <v>-22.68875274584595</v>
+        <v>-29.28381850928671</v>
       </c>
       <c r="F37">
-        <v>0.8628116005278041</v>
+        <v>-1.761342016839443</v>
       </c>
       <c r="G37">
-        <v>-2.250375481638683</v>
+        <v>-7.556668550925894</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.752132383969426</v>
       </c>
       <c r="E38">
-        <v>-21.53936717253711</v>
+        <v>-25.77677804183847</v>
       </c>
       <c r="F38">
-        <v>1.033198491609634</v>
+        <v>-2.032880023109719</v>
       </c>
       <c r="G38">
-        <v>-2.240991187978671</v>
+        <v>-7.295663781979863</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.720541449113425</v>
       </c>
       <c r="E39">
-        <v>-20.51076052948685</v>
+        <v>-26.04128168015248</v>
       </c>
       <c r="F39">
-        <v>0.5023732045890861</v>
+        <v>-1.644222463227232</v>
       </c>
       <c r="G39">
-        <v>-2.199956231156255</v>
+        <v>-5.986535129078849</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.661373839652152</v>
       </c>
       <c r="E40">
-        <v>-20.61773667097005</v>
+        <v>-25.13253468713724</v>
       </c>
       <c r="F40">
-        <v>1.005529363621325</v>
+        <v>-1.192037407224052</v>
       </c>
       <c r="G40">
-        <v>-0.9188032732710658</v>
+        <v>-6.885524211935512</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.584897444664457</v>
       </c>
       <c r="E41">
-        <v>-19.55711824515957</v>
+        <v>-23.67243239826611</v>
       </c>
       <c r="F41">
-        <v>0.5352105168034612</v>
+        <v>-1.29332851650357</v>
       </c>
       <c r="G41">
-        <v>-1.194455415258457</v>
+        <v>-6.992111413072514</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.500274643364372</v>
       </c>
       <c r="E42">
-        <v>-19.42879487720421</v>
+        <v>-24.06093018338415</v>
       </c>
       <c r="F42">
-        <v>0.7882452803974038</v>
+        <v>-0.6888539120675207</v>
       </c>
       <c r="G42">
-        <v>-1.200417394831968</v>
+        <v>-6.222687925933644</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.419584211672623</v>
       </c>
       <c r="E43">
-        <v>-18.36204489758735</v>
+        <v>-24.09495713707779</v>
       </c>
       <c r="F43">
-        <v>0.5899738858025365</v>
+        <v>-1.654181924511091</v>
       </c>
       <c r="G43">
-        <v>-0.7963644907803863</v>
+        <v>-6.638786194329947</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.350090145814666</v>
       </c>
       <c r="E44">
-        <v>-18.70952376514391</v>
+        <v>-23.33852536731054</v>
       </c>
       <c r="F44">
-        <v>0.3565084737323295</v>
+        <v>-1.461302373341046</v>
       </c>
       <c r="G44">
-        <v>-0.5730051767858656</v>
+        <v>-6.954285490935235</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.300210576375019</v>
       </c>
       <c r="E45">
-        <v>-18.10509928239213</v>
+        <v>-23.757970743797</v>
       </c>
       <c r="F45">
-        <v>0.4365726683151101</v>
+        <v>-1.373666072329275</v>
       </c>
       <c r="G45">
-        <v>-1.016606644293435</v>
+        <v>-7.950149359112944</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.271695477858629</v>
       </c>
       <c r="E46">
-        <v>-17.18944636651519</v>
+        <v>-24.08590018906245</v>
       </c>
       <c r="F46">
-        <v>0.8386895417582825</v>
+        <v>-1.480974442422728</v>
       </c>
       <c r="G46">
-        <v>-0.564493688060666</v>
+        <v>-5.823422324137293</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.263525001330342</v>
       </c>
       <c r="E47">
-        <v>-16.544039193994</v>
+        <v>-22.56276607047855</v>
       </c>
       <c r="F47">
-        <v>0.6350552965976912</v>
+        <v>-1.052776421302413</v>
       </c>
       <c r="G47">
-        <v>-0.7156562840827246</v>
+        <v>-5.723407409783858</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.270820439170007</v>
       </c>
       <c r="E48">
-        <v>-16.45710607846875</v>
+        <v>-22.16088211619384</v>
       </c>
       <c r="F48">
-        <v>0.4455861340249715</v>
+        <v>-0.6019399474309909</v>
       </c>
       <c r="G48">
-        <v>-0.9666861394880426</v>
+        <v>-5.566315646403883</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.284010654141599</v>
       </c>
       <c r="E49">
-        <v>-15.58191054937634</v>
+        <v>-22.71406691554883</v>
       </c>
       <c r="F49">
-        <v>0.7450293529933536</v>
+        <v>-1.93048801355188</v>
       </c>
       <c r="G49">
-        <v>-0.5446422976260255</v>
+        <v>-5.597880997805741</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.296030264212296</v>
       </c>
       <c r="E50">
-        <v>-15.05705588341333</v>
+        <v>-21.99761251432129</v>
       </c>
       <c r="F50">
-        <v>0.4463888220382842</v>
+        <v>-1.626139202824119</v>
       </c>
       <c r="G50">
-        <v>-0.6258262814498067</v>
+        <v>-7.193197795121524</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.298037678299415</v>
       </c>
       <c r="E51">
-        <v>-14.971843588011</v>
+        <v>-20.38594672888744</v>
       </c>
       <c r="F51">
-        <v>0.556926996635253</v>
+        <v>-1.755080387641682</v>
       </c>
       <c r="G51">
-        <v>-0.23681121580516</v>
+        <v>-6.695347891571656</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.287057149004005</v>
       </c>
       <c r="E52">
-        <v>-14.68818450464454</v>
+        <v>-20.13838411183612</v>
       </c>
       <c r="F52">
-        <v>0.6473366717115967</v>
+        <v>-1.801032412577179</v>
       </c>
       <c r="G52">
-        <v>-0.09601399868938727</v>
+        <v>-5.601897212994501</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.260212617346917</v>
       </c>
       <c r="E53">
-        <v>-12.27670869692396</v>
+        <v>-19.98097888380351</v>
       </c>
       <c r="F53">
-        <v>0.5864640931168751</v>
+        <v>-1.742438672707559</v>
       </c>
       <c r="G53">
-        <v>-0.7969551106610864</v>
+        <v>-6.639140566258368</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.219177559140159</v>
       </c>
       <c r="E54">
-        <v>-13.02400200614373</v>
+        <v>-18.30968668111066</v>
       </c>
       <c r="F54">
-        <v>0.2193001822348278</v>
+        <v>-1.232611670980575</v>
       </c>
       <c r="G54">
-        <v>-0.8656409215649425</v>
+        <v>-5.944663460758774</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.170074178901231</v>
       </c>
       <c r="E55">
-        <v>-12.05819624063185</v>
+        <v>-19.48689519872262</v>
       </c>
       <c r="F55">
-        <v>0.700757257150734</v>
+        <v>-1.982010809271204</v>
       </c>
       <c r="G55">
-        <v>-0.6244219186223643</v>
+        <v>-6.013608488165827</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.118929638336104</v>
       </c>
       <c r="E56">
-        <v>-12.01358171470828</v>
+        <v>-18.06084703438917</v>
       </c>
       <c r="F56">
-        <v>0.2857311061023341</v>
+        <v>-1.733833592127277</v>
       </c>
       <c r="G56">
-        <v>-0.7901597008114764</v>
+        <v>-7.140471845882807</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.077215519513875</v>
       </c>
       <c r="E57">
-        <v>-11.49160715821415</v>
+        <v>-17.79181945054149</v>
       </c>
       <c r="F57">
-        <v>0.5904369431807015</v>
+        <v>-1.121376839397852</v>
       </c>
       <c r="G57">
-        <v>-1.498782152453835</v>
+        <v>-6.624768815828</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.053346920281844</v>
       </c>
       <c r="E58">
-        <v>-11.23957040884325</v>
+        <v>-18.29486045720955</v>
       </c>
       <c r="F58">
-        <v>0.5312252412285928</v>
+        <v>-1.419863294016</v>
       </c>
       <c r="G58">
-        <v>-1.516100439844585</v>
+        <v>-6.769234438647231</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.057255283105859</v>
       </c>
       <c r="E59">
-        <v>-10.52134990275273</v>
+        <v>-18.09899037095578</v>
       </c>
       <c r="F59">
-        <v>0.7985302900705624</v>
+        <v>-1.546800658086191</v>
       </c>
       <c r="G59">
-        <v>-1.829696627945395</v>
+        <v>-7.150371291327652</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.095303692984614</v>
       </c>
       <c r="E60">
-        <v>-10.45634365837262</v>
+        <v>-17.324530746164</v>
       </c>
       <c r="F60">
-        <v>0.7111209617271587</v>
+        <v>-1.05627875868145</v>
       </c>
       <c r="G60">
-        <v>-2.379291395487706</v>
+        <v>-7.894932962710609</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.170706757724674</v>
       </c>
       <c r="E61">
-        <v>-9.689256389265321</v>
+        <v>-16.80199013041891</v>
       </c>
       <c r="F61">
-        <v>0.6798525773736857</v>
+        <v>-1.482181373728607</v>
       </c>
       <c r="G61">
-        <v>-2.356605029625706</v>
+        <v>-7.846242915990008</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.287137589639176</v>
       </c>
       <c r="E62">
-        <v>-9.927087315674161</v>
+        <v>-16.74046628255071</v>
       </c>
       <c r="F62">
-        <v>0.6706237361390964</v>
+        <v>-0.8185679636718952</v>
       </c>
       <c r="G62">
-        <v>-2.337232697538744</v>
+        <v>-8.333428849471682</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.440452759334087</v>
       </c>
       <c r="E63">
-        <v>-9.586306061174943</v>
+        <v>-16.40918123804557</v>
       </c>
       <c r="F63">
-        <v>0.405619063574701</v>
+        <v>-1.519259098677913</v>
       </c>
       <c r="G63">
-        <v>-2.591694710695241</v>
+        <v>-8.148787949878608</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.628208584597092</v>
       </c>
       <c r="E64">
-        <v>-9.615822654756938</v>
+        <v>-15.82920598646121</v>
       </c>
       <c r="F64">
-        <v>0.2524622144711004</v>
+        <v>-1.985682133600411</v>
       </c>
       <c r="G64">
-        <v>-3.350916880005797</v>
+        <v>-8.583051060827998</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.841908825957431</v>
       </c>
       <c r="E65">
-        <v>-9.228466045088831</v>
+        <v>-14.57550701438568</v>
       </c>
       <c r="F65">
-        <v>0.55401445684701</v>
+        <v>-1.808971485765609</v>
       </c>
       <c r="G65">
-        <v>-2.672665415117658</v>
+        <v>-9.060321142757029</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.073515137269164</v>
       </c>
       <c r="E66">
-        <v>-9.9604666975847</v>
+        <v>-15.13562490744641</v>
       </c>
       <c r="F66">
-        <v>0.3581387007810389</v>
+        <v>-1.777190341989803</v>
       </c>
       <c r="G66">
-        <v>-2.863681728200732</v>
+        <v>-9.208563451591182</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.314371816697455</v>
       </c>
       <c r="E67">
-        <v>-9.04176159022659</v>
+        <v>-16.25047633797276</v>
       </c>
       <c r="F67">
-        <v>-0.07731084858338282</v>
+        <v>-1.810478286071302</v>
       </c>
       <c r="G67">
-        <v>-2.770225975744628</v>
+        <v>-7.911552349909196</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.553484597070034</v>
       </c>
       <c r="E68">
-        <v>-9.320756345365153</v>
+        <v>-16.0226125828548</v>
       </c>
       <c r="F68">
-        <v>0.1921835753041859</v>
+        <v>-2.116820977137601</v>
       </c>
       <c r="G68">
-        <v>-3.018256794644613</v>
+        <v>-8.359576904078896</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.784449129629365</v>
       </c>
       <c r="E69">
-        <v>-8.63252339415342</v>
+        <v>-15.39263392127774</v>
       </c>
       <c r="F69">
-        <v>-0.05229829485585174</v>
+        <v>-2.08125088086139</v>
       </c>
       <c r="G69">
-        <v>-3.311289567232383</v>
+        <v>-8.897772707923696</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.996628487962121</v>
       </c>
       <c r="E70">
-        <v>-9.281222767278191</v>
+        <v>-14.74623048447486</v>
       </c>
       <c r="F70">
-        <v>-0.1747343104592299</v>
+        <v>-2.415546001567756</v>
       </c>
       <c r="G70">
-        <v>-3.035922891520664</v>
+        <v>-9.568575799871896</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.186205331239385</v>
       </c>
       <c r="E71">
-        <v>-8.778716120543043</v>
+        <v>-16.74556534428334</v>
       </c>
       <c r="F71">
-        <v>-0.1569567176277497</v>
+        <v>-2.6906550997115</v>
       </c>
       <c r="G71">
-        <v>-3.289702410592796</v>
+        <v>-8.354855226254855</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.34836342908904</v>
       </c>
       <c r="E72">
-        <v>-8.939703371515723</v>
+        <v>-17.30548398448774</v>
       </c>
       <c r="F72">
-        <v>-0.4408531371803907</v>
+        <v>-2.956899838277886</v>
       </c>
       <c r="G72">
-        <v>-3.095601749243844</v>
+        <v>-8.432459397357283</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.482030255771151</v>
       </c>
       <c r="E73">
-        <v>-9.427057744221207</v>
+        <v>-15.92443979484251</v>
       </c>
       <c r="F73">
-        <v>-0.3830562867522636</v>
+        <v>-2.280850976770348</v>
       </c>
       <c r="G73">
-        <v>-3.587768577052754</v>
+        <v>-8.675102450456659</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.588286343146258</v>
       </c>
       <c r="E74">
-        <v>-10.25358576315319</v>
+        <v>-15.19403316519735</v>
       </c>
       <c r="F74">
-        <v>-0.2213424023777441</v>
+        <v>-2.249956186115537</v>
       </c>
       <c r="G74">
-        <v>-3.14041667330274</v>
+        <v>-9.358200279588099</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.666288034769756</v>
       </c>
       <c r="E75">
-        <v>-10.64652145279874</v>
+        <v>-16.03730295253568</v>
       </c>
       <c r="F75">
-        <v>-0.4263268864048985</v>
+        <v>-1.962643579393751</v>
       </c>
       <c r="G75">
-        <v>-2.962226655295535</v>
+        <v>-6.969001769629345</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.71827804454519</v>
       </c>
       <c r="E76">
-        <v>-11.05195120223146</v>
+        <v>-17.96276481585704</v>
       </c>
       <c r="F76">
-        <v>-0.4550960863041253</v>
+        <v>-2.780368946169491</v>
       </c>
       <c r="G76">
-        <v>-2.647560788966346</v>
+        <v>-6.456940895505522</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.740186871406459</v>
       </c>
       <c r="E77">
-        <v>-10.45364468786405</v>
+        <v>-18.33278189854978</v>
       </c>
       <c r="F77">
-        <v>-0.9483242620138126</v>
+        <v>-3.370061334302584</v>
       </c>
       <c r="G77">
-        <v>-2.705202008101112</v>
+        <v>-7.156192178374106</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.732408457068354</v>
       </c>
       <c r="E78">
-        <v>-11.25839527529314</v>
+        <v>-16.80136520100585</v>
       </c>
       <c r="F78">
-        <v>-0.7571486625913258</v>
+        <v>-2.350850507409114</v>
       </c>
       <c r="G78">
-        <v>-2.03039254462883</v>
+        <v>-9.338798416507101</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.694354065081946</v>
       </c>
       <c r="E79">
-        <v>-11.42598956984301</v>
+        <v>-19.08444518518695</v>
       </c>
       <c r="F79">
-        <v>-0.8214548240706515</v>
+        <v>-2.701461152481019</v>
       </c>
       <c r="G79">
-        <v>-1.700980868611497</v>
+        <v>-9.110694456137624</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.632210902766568</v>
       </c>
       <c r="E80">
-        <v>-12.86500275526042</v>
+        <v>-19.13113375220603</v>
       </c>
       <c r="F80">
-        <v>-1.025775785808164</v>
+        <v>-3.062602832344714</v>
       </c>
       <c r="G80">
-        <v>-1.911061078954945</v>
+        <v>-9.708880833753753</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.55098980693172</v>
       </c>
       <c r="E81">
-        <v>-12.6950808250706</v>
+        <v>-19.6272733644864</v>
       </c>
       <c r="F81">
-        <v>-1.118258036126311</v>
+        <v>-2.743865279830326</v>
       </c>
       <c r="G81">
-        <v>-1.738278514077705</v>
+        <v>-7.368789085653648</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.45338513051748</v>
       </c>
       <c r="E82">
-        <v>-13.80385051500465</v>
+        <v>-19.80347175965084</v>
       </c>
       <c r="F82">
-        <v>-1.14936820230585</v>
+        <v>-3.334439050879997</v>
       </c>
       <c r="G82">
-        <v>-1.805697773459616</v>
+        <v>-6.548437758690637</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.341288456546109</v>
       </c>
       <c r="E83">
-        <v>-14.76790376107557</v>
+        <v>-22.26721974284195</v>
       </c>
       <c r="F83">
-        <v>-1.241563009135226</v>
+        <v>-3.575067355882211</v>
       </c>
       <c r="G83">
-        <v>-2.165959494578849</v>
+        <v>-5.52378773377192</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.210586311416513</v>
       </c>
       <c r="E84">
-        <v>-15.65745455277229</v>
+        <v>-21.51004530333745</v>
       </c>
       <c r="F84">
-        <v>-1.508555763466341</v>
+        <v>-3.26659658895812</v>
       </c>
       <c r="G84">
-        <v>-1.192880428909924</v>
+        <v>-6.148282945851676</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.061334389132103</v>
       </c>
       <c r="E85">
-        <v>-17.06675642022538</v>
+        <v>-23.3340195356729</v>
       </c>
       <c r="F85">
-        <v>-1.593426145720164</v>
+        <v>-2.970688842064886</v>
       </c>
       <c r="G85">
-        <v>-0.1936729959631404</v>
+        <v>-5.785724369640832</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.889174158680774</v>
       </c>
       <c r="E86">
-        <v>-17.83289270979106</v>
+        <v>-24.7419673893977</v>
       </c>
       <c r="F86">
-        <v>-1.770135965187563</v>
+        <v>-3.53274772200799</v>
       </c>
       <c r="G86">
-        <v>-0.5475100852689802</v>
+        <v>-4.826419872078456</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.696369423282015</v>
       </c>
       <c r="E87">
-        <v>-19.10714189691339</v>
+        <v>-23.67139084924435</v>
       </c>
       <c r="F87">
-        <v>-1.752782496466316</v>
+        <v>-3.168661196027343</v>
       </c>
       <c r="G87">
-        <v>-0.6165404244365781</v>
+        <v>-6.070937991252445</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.484979777751067</v>
       </c>
       <c r="E88">
-        <v>-20.71719554560051</v>
+        <v>-25.8679543375089</v>
       </c>
       <c r="F88">
-        <v>-2.041423804502192</v>
+        <v>-3.607670240121594</v>
       </c>
       <c r="G88">
-        <v>-0.6261150289470377</v>
+        <v>-5.282713104577957</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.259956802659561</v>
       </c>
       <c r="E89">
-        <v>-21.38696137980897</v>
+        <v>-26.23869144756886</v>
       </c>
       <c r="F89">
-        <v>-2.11142664861057</v>
+        <v>-3.737463814996638</v>
       </c>
       <c r="G89">
-        <v>0.02917772868966641</v>
+        <v>-4.525574510957648</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.030038737062228</v>
       </c>
       <c r="E90">
-        <v>-23.28998918289633</v>
+        <v>-28.3939190250914</v>
       </c>
       <c r="F90">
-        <v>-2.092485199578157</v>
+        <v>-3.913418991760086</v>
       </c>
       <c r="G90">
-        <v>-0.1114423024618963</v>
+        <v>-6.39839077799879</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.801916150061948</v>
       </c>
       <c r="E91">
-        <v>-25.13574084673467</v>
+        <v>-30.1797816201783</v>
       </c>
       <c r="F91">
-        <v>-2.380827466981623</v>
+        <v>-3.348749097763358</v>
       </c>
       <c r="G91">
-        <v>-0.05804698402505247</v>
+        <v>-5.145203671464748</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.588371647726759</v>
       </c>
       <c r="E92">
-        <v>-27.29051557685644</v>
+        <v>-30.68670579330793</v>
       </c>
       <c r="F92">
-        <v>-2.846052682639673</v>
+        <v>-3.763342012660094</v>
       </c>
       <c r="G92">
-        <v>-0.15585691749054</v>
+        <v>-5.870055044940121</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.398146134537763</v>
       </c>
       <c r="E93">
-        <v>-29.97729996187334</v>
+        <v>-33.72392387517139</v>
       </c>
       <c r="F93">
-        <v>-2.7780635996875</v>
+        <v>-2.780293564735837</v>
       </c>
       <c r="G93">
-        <v>0.01482894681021467</v>
+        <v>-6.398512183196489</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.243425175691521</v>
       </c>
       <c r="E94">
-        <v>-31.16398883982036</v>
+        <v>-36.16741146565219</v>
       </c>
       <c r="F94">
-        <v>-2.835490998253979</v>
+        <v>-3.977263752596052</v>
       </c>
       <c r="G94">
-        <v>-0.1957598528749472</v>
+        <v>-6.167186063255637</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.13371122447701</v>
       </c>
       <c r="E95">
-        <v>-34.04287562071664</v>
+        <v>-36.47338234045444</v>
       </c>
       <c r="F95">
-        <v>-3.118376809575205</v>
+        <v>-4.161529939511788</v>
       </c>
       <c r="G95">
-        <v>-0.1783496912805335</v>
+        <v>-5.991053371166204</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.077066902597732</v>
       </c>
       <c r="E96">
-        <v>-35.67728113838</v>
+        <v>-39.65184126238013</v>
       </c>
       <c r="F96">
-        <v>-2.948294757697604</v>
+        <v>-4.391961870152944</v>
       </c>
       <c r="G96">
-        <v>-1.187177665839609</v>
+        <v>-5.657536886978005</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.076236267121664</v>
       </c>
       <c r="E97">
-        <v>-37.90483071004203</v>
+        <v>-42.53386854000073</v>
       </c>
       <c r="F97">
-        <v>-3.367543097398074</v>
+        <v>-4.877172277770935</v>
       </c>
       <c r="G97">
-        <v>-0.8971078363200174</v>
+        <v>-6.934394725841882</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.133457222379331</v>
       </c>
       <c r="E98">
-        <v>-40.48534765975793</v>
+        <v>-43.32291211533422</v>
       </c>
       <c r="F98">
-        <v>-3.3067144222757</v>
+        <v>-4.562387694502705</v>
       </c>
       <c r="G98">
-        <v>-1.311870647541627</v>
+        <v>-6.150924329207029</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.237949739381064</v>
       </c>
       <c r="E99">
-        <v>-43.29642054238934</v>
+        <v>-44.56473742856163</v>
       </c>
       <c r="F99">
-        <v>-3.43746558986838</v>
+        <v>-4.926093171478065</v>
       </c>
       <c r="G99">
-        <v>-1.4296172832023</v>
+        <v>-7.17992525391357</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.390519411091305</v>
       </c>
       <c r="E100">
-        <v>-44.77685567955491</v>
+        <v>-47.50823647659934</v>
       </c>
       <c r="F100">
-        <v>-3.331792417028053</v>
+        <v>-4.374874307367995</v>
       </c>
       <c r="G100">
-        <v>-2.003030438044621</v>
+        <v>-5.888981130894998</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.558151719078483</v>
       </c>
       <c r="E101">
-        <v>-47.19744956968993</v>
+        <v>-48.74629296733387</v>
       </c>
       <c r="F101">
-        <v>-3.836822343125424</v>
+        <v>-5.36634890851353</v>
       </c>
       <c r="G101">
-        <v>-2.237992151473338</v>
+        <v>-6.583615735029444</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.756371226112811</v>
       </c>
       <c r="E102">
-        <v>-49.85767332253334</v>
+        <v>-52.25418365577706</v>
       </c>
       <c r="F102">
-        <v>-3.457029971187699</v>
+        <v>-4.977784125780157</v>
       </c>
       <c r="G102">
-        <v>-2.588849891603202</v>
+        <v>-6.935828619663359</v>
       </c>
     </row>
   </sheetData>
